--- a/template_invoice.xlsx
+++ b/template_invoice.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="請求" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="タイトル">#REF!</definedName>
@@ -130,7 +130,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -469,6 +469,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top style="hair"/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top style="hair"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <bottom/>
+    </border>
+    <border>
+      <right style="hair"/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
@@ -481,7 +528,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -668,6 +715,23 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1005,7 +1069,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B1:M48"/>
@@ -1190,9 +1253,9 @@
       <c r="G11" s="1" t="n"/>
       <c r="H11" s="1" t="n"/>
       <c r="I11" s="1" t="n"/>
-      <c r="J11" s="64" t="n"/>
-      <c r="K11" s="58" t="n"/>
-      <c r="L11" s="49" t="n"/>
+      <c r="J11" s="71" t="n"/>
+      <c r="K11" s="72" t="n"/>
+      <c r="L11" s="73" t="n"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="32">
       <c r="B12" s="1" t="n"/>
@@ -1201,9 +1264,9 @@
       <c r="G12" s="1" t="n"/>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="1" t="n"/>
-      <c r="J12" s="65" t="n"/>
-      <c r="K12" s="50" t="n"/>
-      <c r="L12" s="50" t="n"/>
+      <c r="J12" s="79" t="n"/>
+      <c r="K12" s="74" t="n"/>
+      <c r="L12" s="74" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
@@ -1220,9 +1283,9 @@
       <c r="E13" s="38" t="n"/>
       <c r="F13" s="38" t="n"/>
       <c r="G13" s="1" t="n"/>
-      <c r="J13" s="65" t="n"/>
-      <c r="K13" s="51" t="n"/>
-      <c r="L13" s="51" t="n"/>
+      <c r="J13" s="79" t="n"/>
+      <c r="K13" s="75" t="n"/>
+      <c r="L13" s="75" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="32">
       <c r="B14" s="1" t="n"/>
@@ -1727,12 +1790,12 @@
     <mergeCell ref="I14:L14"/>
     <mergeCell ref="K24:L24"/>
     <mergeCell ref="K33:L33"/>
+    <mergeCell ref="L12:L13"/>
     <mergeCell ref="C45:G45"/>
     <mergeCell ref="K26:L26"/>
     <mergeCell ref="C29:G29"/>
     <mergeCell ref="K35:L35"/>
     <mergeCell ref="C47:G47"/>
-    <mergeCell ref="L11:L13"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="C31:G31"/>
     <mergeCell ref="C40:G40"/>
@@ -1757,13 +1820,13 @@
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="K43:L43"/>
     <mergeCell ref="C46:G46"/>
+    <mergeCell ref="J12:J13"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="I7:L7"/>
     <mergeCell ref="C39:G39"/>
     <mergeCell ref="K17:L17"/>
     <mergeCell ref="C32:G32"/>
     <mergeCell ref="C38:G38"/>
-    <mergeCell ref="J11:J13"/>
     <mergeCell ref="K19:L19"/>
     <mergeCell ref="K16:L16"/>
     <mergeCell ref="K25:L25"/>
@@ -1782,7 +1845,6 @@
     <mergeCell ref="K31:L31"/>
     <mergeCell ref="K46:L46"/>
     <mergeCell ref="K40:L40"/>
-    <mergeCell ref="K11:K13"/>
     <mergeCell ref="K23:L23"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="J1:L1"/>
@@ -1797,6 +1859,7 @@
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="K12:K13"/>
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="K22:L22"/>
     <mergeCell ref="C43:G43"/>

--- a/template_invoice.xlsx
+++ b/template_invoice.xlsx
@@ -130,7 +130,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -516,6 +516,13 @@
     <border>
       <right style="hair"/>
     </border>
+    <border>
+      <left/>
+      <right style="hair"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
@@ -528,7 +535,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -732,6 +739,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1076,9 +1084,9 @@
   <cols>
     <col width="13" customWidth="1" style="32" min="1" max="1"/>
     <col width="0.88671875" customWidth="1" style="32" min="2" max="2"/>
-    <col width="11.109375" customWidth="1" style="32" min="3" max="3"/>
+    <col width="8.710000000000001" customWidth="1" style="32" min="3" max="3"/>
     <col width="6.5546875" customWidth="1" style="32" min="4" max="4"/>
-    <col width="20.6640625" customWidth="1" style="32" min="5" max="5"/>
+    <col width="23.0634375" customWidth="1" style="32" min="5" max="5"/>
     <col width="6.77734375" customWidth="1" style="32" min="6" max="6"/>
     <col width="10.44140625" customWidth="1" style="32" min="7" max="7"/>
     <col width="6.21875" customWidth="1" style="32" min="8" max="8"/>
@@ -1265,8 +1273,8 @@
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="1" t="n"/>
       <c r="J12" s="79" t="n"/>
-      <c r="K12" s="74" t="n"/>
-      <c r="L12" s="74" t="n"/>
+      <c r="K12" s="77" t="n"/>
+      <c r="L12" s="77" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
@@ -1283,9 +1291,9 @@
       <c r="E13" s="38" t="n"/>
       <c r="F13" s="38" t="n"/>
       <c r="G13" s="1" t="n"/>
-      <c r="J13" s="79" t="n"/>
-      <c r="K13" s="75" t="n"/>
-      <c r="L13" s="75" t="n"/>
+      <c r="J13" s="80" t="n"/>
+      <c r="K13" s="78" t="n"/>
+      <c r="L13" s="78" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="32">
       <c r="B14" s="1" t="n"/>

--- a/template_invoice.xlsx
+++ b/template_invoice.xlsx
@@ -34,88 +34,88 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="11"/>
       <u val="single"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <b val="1"/>
       <sz val="16"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="16"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="24"/>
       <u val="single"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="17"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="BIZ UDPゴシック"/>
       <charset val="128"/>
       <family val="3"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="BIZ UDPゴシック"/>
       <charset val="128"/>
       <family val="3"/>
       <sz val="6"/>
     </font>
     <font>
-      <name val="ＭＳ 明朝"/>
+      <name val="BIZ UD明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <b val="1"/>
